--- a/docs/downloads/04/tbl_cm_act_sex_marovoay_maroala.xlsx
+++ b/docs/downloads/04/tbl_cm_act_sex_marovoay_maroala.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -394,14 +394,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E2">
-        <v>22.7</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="3">
@@ -417,14 +417,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E3">
-        <v>18.2</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="4">
@@ -440,14 +440,8 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>7</v>
-      </c>
-      <c r="E4">
-        <v>31.8</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -486,14 +480,8 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Éleveur</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>4.5</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -509,14 +497,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="D7">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="E7">
-        <v>33</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="8">
@@ -532,14 +520,8 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Commerçant</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
-      <c r="E8">
-        <v>2.1</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -555,7 +537,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D9">
@@ -578,60 +560,54 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="D10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D11">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="E11">
-        <v>19.3</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Commerçant</t>
-        </is>
-      </c>
-      <c r="D12">
-        <v>17</v>
-      </c>
-      <c r="E12">
-        <v>14.9</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -647,14 +623,8 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>37</v>
-      </c>
-      <c r="E13">
-        <v>32.5</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -670,14 +640,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="D14">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E14">
-        <v>30.7</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="15">
@@ -693,14 +663,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Éleveur</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D15">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="E15">
-        <v>2.6</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="16">
@@ -711,19 +681,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="D16">
-        <v>71</v>
+        <v>5</v>
       </c>
       <c r="E16">
-        <v>17.5</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="17">
@@ -734,19 +704,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D17">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="E17">
-        <v>1.2</v>
+        <v>30.7</v>
       </c>
     </row>
     <row r="18">
@@ -757,19 +727,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="D18">
-        <v>267</v>
+        <v>8</v>
       </c>
       <c r="E18">
-        <v>65.90000000000001</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -785,14 +755,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="D19">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="E19">
-        <v>14.8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="20">
@@ -808,14 +778,106 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Éleveur</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E20">
-        <v>0.5</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>267</v>
+      </c>
+      <c r="E21">
+        <v>65.90000000000001</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
+      </c>
+      <c r="D22">
+        <v>20</v>
+      </c>
+      <c r="E22">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>60</v>
+      </c>
+      <c r="E23">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="D24">
+        <v>14</v>
+      </c>
+      <c r="E24">
+        <v>3.5</v>
       </c>
     </row>
   </sheetData>
